--- a/reports/pro-oil/pro-oil-refunds-report.xlsx
+++ b/reports/pro-oil/pro-oil-refunds-report.xlsx
@@ -36426,7 +36426,7 @@
         <x:v>1137</x:v>
       </x:c>
       <x:c r="H492" s="1">
-        <x:v>3500</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:8">

--- a/reports/pro-oil/pro-oil-refunds-report.xlsx
+++ b/reports/pro-oil/pro-oil-refunds-report.xlsx
@@ -41141,7 +41141,7 @@
         <x:v>1514</x:v>
       </x:c>
       <x:c r="H666" s="1">
-        <x:v>14500</x:v>
+        <x:v>19500</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:8">
